--- a/src/Data/polio_results.xlsx
+++ b/src/Data/polio_results.xlsx
@@ -7,7 +7,9 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="general_risk" sheetId="1" r:id="rId1"/>
+    <sheet name="population_immunity" sheetId="2" r:id="rId2"/>
+    <sheet name="quality_of_surveillance" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,344 +353,993 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ADMIN1 GEO_ID</t>
+          <t>Subnational level</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>GEO_ID</t>
+          <t>Districts</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ADMIN1</t>
+          <t>Population Immunity</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ADMIN2</t>
+          <t>Surveillance Quality</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>POB1</t>
+          <t>Health determinants</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>POB5</t>
+          <t>Outbreak</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>POB15</t>
+          <t>Risk points</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>pfa</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>immunity_score</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>surveillance_score</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>determinants_score</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>outbreaks_score</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>total_score</t>
+          <t>Risk level</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>BELIZE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BLZ.1_1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BELIZE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>BELIZE</t>
-        </is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>25</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>25227</v>
+        <v>45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="I2">
-        <v>19</v>
-      </c>
-      <c r="J2">
-        <v>21</v>
-      </c>
-      <c r="K2">
-        <v>10</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>50</v>
+          <t>Medium</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>BELIZE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BLZ.2_1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>BELIZE</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
           <t>CAYO</t>
         </is>
       </c>
+      <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
       <c r="G3">
+        <v>47</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COROZAL</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>47</v>
+      </c>
+      <c r="D4">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>79</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ORANGE WALK</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>39</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>53</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>STANN CREEK</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>47</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>79</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TOLEDO</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>62</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Subnational level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>POB1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>POB5</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>POB15</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Polio 3 coverage 2020 (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Polio 3 coverage 2021 (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Polio 3 coverage 2022 (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Polio 3 coverage 2023 (%)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Polio 3 coverage 2024 (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Polio3 (score)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>IPV2 coverage</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>IPV2 (score)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Polio vaccination campaign with coverage ≥95%</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Polio vaccination campaign with coverage ≥95% (score)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Total Risk Points</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Risk level</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>25227</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2">
+        <v>93</v>
+      </c>
+      <c r="H2">
+        <v>90</v>
+      </c>
+      <c r="I2">
+        <v>89</v>
+      </c>
+      <c r="J2">
+        <v>76</v>
+      </c>
+      <c r="K2">
+        <v>22</v>
+      </c>
+      <c r="L2">
+        <v>101</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>25</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CAYO</t>
+        </is>
+      </c>
+      <c r="E3">
         <v>10813</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="F3">
+        <v>99</v>
+      </c>
+      <c r="G3">
+        <v>96</v>
+      </c>
+      <c r="H3">
+        <v>90</v>
       </c>
       <c r="I3">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="J3">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="K3">
         <v>12</v>
       </c>
       <c r="L3">
+        <v>104</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="O3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>47</v>
+      <c r="P3">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>BELIZE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BLZ.3_1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>BELIZE</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
           <t>COROZAL</t>
         </is>
       </c>
+      <c r="E4">
+        <v>42579</v>
+      </c>
+      <c r="F4">
+        <v>96</v>
+      </c>
       <c r="G4">
-        <v>42579</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>93</v>
+      </c>
+      <c r="H4">
+        <v>78</v>
+      </c>
+      <c r="I4">
+        <v>74</v>
+      </c>
+      <c r="J4">
+        <v>60</v>
+      </c>
+      <c r="K4">
+        <v>33</v>
+      </c>
+      <c r="L4">
+        <v>81</v>
+      </c>
+      <c r="M4">
+        <v>6</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I4">
+      <c r="O4">
+        <v>8</v>
+      </c>
+      <c r="P4">
         <v>47</v>
       </c>
-      <c r="J4">
-        <v>20</v>
-      </c>
-      <c r="K4">
-        <v>12</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>79</v>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>BELIZE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BLZ.4_1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>BELIZE</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
           <t>ORANGE WALK</t>
         </is>
       </c>
+      <c r="E5">
+        <v>77422</v>
+      </c>
+      <c r="F5">
+        <v>91</v>
+      </c>
       <c r="G5">
-        <v>77422</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
+        <v>94</v>
+      </c>
+      <c r="H5">
+        <v>85</v>
       </c>
       <c r="I5">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="J5">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M5">
-        <v>56</v>
+        <v>3</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O5">
+        <v>8</v>
+      </c>
+      <c r="P5">
+        <v>39</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>BELIZE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BLZ.5_1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>BELIZE</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
           <t>STANN CREEK</t>
         </is>
       </c>
+      <c r="E6">
+        <v>29805</v>
+      </c>
+      <c r="F6">
+        <v>93</v>
+      </c>
       <c r="G6">
-        <v>29805</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>90</v>
+      </c>
+      <c r="H6">
+        <v>77</v>
+      </c>
+      <c r="I6">
+        <v>71</v>
+      </c>
+      <c r="J6">
+        <v>75</v>
+      </c>
+      <c r="K6">
+        <v>36</v>
+      </c>
+      <c r="L6">
+        <v>93</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I6">
+      <c r="O6">
+        <v>8</v>
+      </c>
+      <c r="P6">
         <v>47</v>
       </c>
-      <c r="J6">
-        <v>20</v>
-      </c>
-      <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>79</v>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>BELIZE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BLZ.6_1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>BELIZE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
           <t>TOLEDO</t>
         </is>
       </c>
+      <c r="E7">
+        <v>9546</v>
+      </c>
+      <c r="F7">
+        <v>89</v>
+      </c>
       <c r="G7">
-        <v>9546</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>91</v>
+      </c>
+      <c r="H7">
+        <v>88</v>
+      </c>
+      <c r="I7">
+        <v>86</v>
+      </c>
+      <c r="J7">
+        <v>81</v>
+      </c>
+      <c r="K7">
+        <v>27</v>
+      </c>
+      <c r="L7">
+        <v>104</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>30</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Subnational level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total Risk Points</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Proportion of reporting units that sent information in all weeks</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Notifying units score</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AFP rate</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>AFP rate score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Proportion of AFP cases with timely notification (before 14 days after the onset of paralysis)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Timely notification score</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Proportion of AFP cases that were investigated in less than 48 hours</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Timely investigation score</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Proportion of cases with adequate sample</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adequate sample score</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Proportion of cases with 60-day follow-up</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Follow-up score</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Institutional active case searches in at least one health care facility</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Case searches score</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Risk level</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>75</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>0.25</v>
+      </c>
+      <c r="H2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
+      <c r="L2">
+        <v>100</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Na</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CAYO</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>75</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I7">
-        <v>30</v>
-      </c>
-      <c r="J7">
+      <c r="Q3">
+        <v>12</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COROZAL</t>
+        </is>
+      </c>
+      <c r="C4">
         <v>20</v>
       </c>
-      <c r="K7">
+      <c r="D4">
+        <v>75</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q4">
         <v>12</v>
       </c>
-      <c r="L7">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ORANGE WALK</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>75</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>0.77</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="M7">
-        <v>62</v>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>STANN CREEK</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>75</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q6">
+        <v>12</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TOLEDO</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>75</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q7">
+        <v>12</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
       </c>
     </row>
   </sheetData>
